--- a/data_extactor/batch_10_fa/batch_0101_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0101_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | ایمنی و امنیت عمومی | فیزیک | جغرافیا | مهندسی و فناوری | امور اداری و مدیریت | مخابرات | زبان انگلیسی | کامپیوتر و الکترونیک | پرسنل و منابع انسانی</t>
+          <t>ریاضیات | ایمنی و امنیت عمومی | فیزیک | جغرافیا | مهندسی و فناوری | مدیریت و اداره | مخابرات | زبان انگلیسی | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | اشتراک زمانی | تجسم | استدلال ریاضی | سهولت در کار با اعداد | جهت‌یابی فضایی | زمان عکس‌العمل</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | استدلال ریاضی | توانایی عددی | جهت‌گیری فضایی | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، زیر سرپناه</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، زیر سقف</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیت حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و اجرایی | متخصصان لجستیک | مدیران حمل و نقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مخابرات | کامپیوتر و الکترونیک | ایمنی و امنیت عمومی | امور اداری و مدیریت | جغرافیا | زبان انگلیسی | حمل و نقل | مهندسی و فناوری | ارتباطات و رسانه | پرسنل و منابع انسانی</t>
+          <t>مخابرات | رایانه و الکترونیک | ایمنی و امنیت عمومی | مدیریت و اداره | جغرافیا | زبان انگلیسی | حمل و نقل | مهندسی و فناوری | ارتباطات و رسانه | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | اشتراک زمانی | تجسم | توجه شنیداری | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | توجه شنیداری | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | داخل ساختمان، محیط با دمای کنترل‌شده | صرف زمان به صورت نشسته | اهمیت تکرار وظایف مشابه | درجه اتوماسیون | نامه‌ها و یادداشت‌های مکتوب</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | میزان خودکارسازی | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواگرد | تکنسین‌های اویونیک | مهندسان هوافضا | تکنسین‌ها و فناوران مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل و نقل، انبارداری و توزیع | متخصصان لجستیک | مدیران کل و اجرایی | مدیران ارشد اجرایی | سرپرستان رده اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | افسران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگران امنیت حمل و نقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
+          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های هوانوردی | مهندسان هوافضا | تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل‌ونقل، انبارداری و توزیع | لجستیسین‌ها | مدیران عمومی و عملیات | مدیران ارشد اجرایی | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگران امنیتی حمل و نقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | امور اداری و مدیریت | مخابرات | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | حمل و نقل | روانشناسی</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | مدیریت و اداره | مخابرات | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | حمل و نقل | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | اشتراک زمانی | تجسم | جهت‌یابی فضایی | استقامت | قدرت استاتیک | هماهنگی کلی بدن | زمان عکس‌العمل</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع | صرف زمان برای پیاده‌روی یا دویدن | صرف زمان به صورت ایستاده</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیت حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و اجرایی | متخصصان لجستیک | مدیران حمل و نقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | زبان خارجی | امور اداری و مدیریت | مخابرات | جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | آموزش و پرورش | روانشناسی | حمل و نقل</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | زبان خارجی | مدیریت و اداره | مخابرات | جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | اشتراک زمانی | تجسم | جهت‌یابی فضایی | استقامت | قدرت استاتیک | هماهنگی کلی بدن | زمان عکس‌العمل | حفظ کردن</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | زمان عکس‌العمل | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع | صرف زمان برای پیاده‌روی یا دویدن | قرار گرفتن در معرض ارتفاعات بالا</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض ارتفاعات بالا</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیت حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و اجرایی | متخصصان لجستیک | مدیران حمل و نقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | امور اداری و مدیریت | جغرافیا | مخابرات | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | حمل و نقل</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | جغرافیا | مخابرات | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | حمل و نقل</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | اشتراک زمانی | تجسم | جهت‌یابی فضایی | زمان عکس‌العمل | استقامت</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | زمان عکس‌العمل | استقامت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیت حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و اجرایی | متخصصان لجستیک | مدیران حمل و نقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | مخابرات | امور اداری و مدیریت | آموزش و پرورش | زبان انگلیسی | کامپیوتر و الکترونیک | پرسنل و منابع انسانی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | مخابرات | مدیریت و اداره | آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | اشتراک زمانی | تجسم | توجه شنیداری | زمان عکس‌العمل | زبردستی دستی | دقت کنترل</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | توجه شنیداری | زمان عکس‌العمل | مهارت دستی | دقت کنترل</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض شرایط خطرناک | صرف زمان به صورت نشسته</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواگرد | تکنسین‌های اویونیک | مهندسان هوافضا | تکنسین‌ها و فناوران مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل و نقل، انبارداری و توزیع | متخصصان لجستیک | مدیران کل و اجرایی | مدیران ارشد اجرایی | سرپرستان رده اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | افسران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگران امنیت حمل و نقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
+          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های هوانوردی | مهندسان هوافضا | تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل‌ونقل، انبارداری و توزیع | لجستیسین‌ها | مدیران عمومی و عملیات | مدیران ارشد اجرایی | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگران امنیتی حمل و نقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Computerized maintenance management system CMMS | نرم‌افزار رادار | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار شبیه‌سازی و مدل‌سازی | نرم‌افزار ناوبری | نرم‌افزار نقشه‌برداری دیجیتال | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI | Microsoft PowerPoint | نرم‌افزار پایگاه داده ماهواره‌ای</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار رادار | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار شبیه‌سازی و مدل‌سازی | نرم‌افزار ناوبری | نرم‌افزار نقشه‌برداری دیجیتال | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI | Microsoft PowerPoint | نرم‌افزار پایگاه داده ماهواره‌ای</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مکانیک | مهندسی و فناوری | امور اداری و مدیریت | آموزش و پرورش | فیزیک | زبان انگلیسی | کامپیوتر و الکترونیک | پرسنل و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | مهندسی و فناوری | مدیریت و اداره | آموزش و پرورش | فیزیک | زبان انگلیسی | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | اشتراک زمانی | تجسم | زبردستی دستی | ثبات بازو-دست | دقت کنترل | زمان عکس‌العمل | قدرت استاتیک</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | مهارت دستی | ثبات دست و بازو | دقت کنترل | زمان عکس‌العمل | قدرت ایستا</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های خدمات و مکانیک‌های هواگرد | تکنسین‌های اویونیک | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل | دکل‌بندها | اپراتورهای جرثقیل و دکل | اپراتورهای ماشین‌آلات مهندسی و سایر تجهیزات ساختمانی | مهندسان کشتی | ملوانان و روغن‌کاران دریایی | کاپیتان‌ها، افسران دوم و خلبانان شناورهای آبی | متخصصان عملیات فرودگاه | متخصصان لجستیک | مدیران حمل و نقل، انبارداری و توزیع | مدیران کل و اجرایی | متخصصان بهداشت و ایمنی شغلی | متخصصان آموزش و توسعه | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های هوانوردی | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | ریگرها | اپراتورهای جرثقیل و تاور | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مهندسان کشتی | ملوانان و روغن‌کاران دریایی | ناخدایان، افسران دوم و راهنمایان شناورهای دریایی | متخصصان عملیات فرودگاه | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عمومی و عملیات | متخصصان بهداشت و ایمنی شغلی | متخصصان آموزش و توسعه | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | امور اداری و مدیریت | آموزش و پرورش | جغرافیا | مخابرات | زبان انگلیسی | پرسنل و منابع انسانی | حمل و نقل | روانشناسی</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | آموزش و پرورش | جغرافیا | مخابرات | زبان انگلیسی | پرسنل و منابع انسانی | حمل و نقل | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | اشتراک زمانی | تجسم | جهت‌یابی فضایی | زمان عکس‌العمل | استقامت | قدرت استاتیک</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | زمان عکس‌العمل | استقامت | قدرت ایستا</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیت حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و اجرایی | متخصصان لجستیک | مدیران حمل و نقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | گوش‌دادن فعال | تفکر انتقادی | سخن‌گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>حمل و نقل | مکانیک | مخابرات | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | زبان انگلیسی | جغرافیا | مهندسی و فناوری</t>
+          <t>حمل و نقل | مکانیک | مخابرات | ایمنی و امنیت عمومی | رایانه و الکترونیک | زبان انگلیسی | جغرافیا | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی به اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌یابی فضایی | استقامت | قدرت استاتیک | هماهنگی کلی بدن | درک عمق | اشتراک زمانی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض ارتعاش کل بدن | صرف زمان به صورت نشسته | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض ارتعاش کل بدن | صرف زمان برای نشستن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواگرد | تکنسین‌های اویونیک | مهندسان هوافضا | تکنسین‌ها و فناوران مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل و نقل، انبارداری و توزیع | متخصصان لجستیک | مدیران کل و اجرایی | مدیران ارشد اجرایی | سرپرستان رده اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | افسران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگران امنیت حمل و نقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
+          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های هوانوردی | مهندسان هوافضا | تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل‌ونقل، انبارداری و توزیع | لجستیسین‌ها | مدیران عمومی و عملیات | مدیران ارشد اجرایی | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگران امنیتی حمل و نقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Computerized maintenance management system CMMS | نرم‌افزار رادار | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار شبیه‌سازی و مدل‌سازی | نرم‌افزار ناوبری | نرم‌افزار نقشه‌برداری دیجیتال | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI | Microsoft PowerPoint | نرم‌افزار پایگاه داده ماهواره‌ای</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار رادار | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار شبیه‌سازی و مدل‌سازی | نرم‌افزار ناوبری | نرم‌افزار نقشه‌برداری دیجیتال | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI | Microsoft PowerPoint | نرم‌افزار پایگاه داده ماهواره‌ای</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | گوش‌دادن فعال | تفکر انتقادی | سخن‌گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل و نقل | فیزیک | زبان انگلیسی | کامپیوتر و الکترونیک</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل و نقل | فیزیک | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی به اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌یابی فضایی | استقامت | قدرت استاتیک | هماهنگی کلی بدن | درک عمق | اشتراک زمانی | زبردستی دستی | ثبات بازو-دست | دقت کنترل</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | مهارت دستی | ثبات دست و بازو | دقت کنترل</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک, دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای خم شدن یا پیچاندن بدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های خدمات و مکانیک‌های هواگرد | تکنسین‌های اویونیک | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل | دکل‌بندها | اپراتورهای جرثقیل و دکل | اپراتورهای ماشین‌آلات مهندسی و سایر تجهیزات ساختمانی | مهندسان کشتی | ملوانان و روغن‌کاران دریایی | کاپیتان‌ها، افسران دوم و خلبانان شناورهای آبی | متخصصان عملیات فرودگاه | متخصصان لجستیک | مدیران حمل و نقل، انبارداری و توزیع | مدیران کل و اجرایی | متخصصان بهداشت و ایمنی شغلی | متخصصان آموزش و توسعه | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های هوانوردی | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | ریگرها | اپراتورهای جرثقیل و تاور | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مهندسان کشتی | ملوانان و روغن‌کاران دریایی | ناخدایان، افسران دوم و راهنمایان شناورهای دریایی | متخصصان عملیات فرودگاه | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عمومی و عملیات | متخصصان بهداشت و ایمنی شغلی | متخصصان آموزش و توسعه | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0101_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0101_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | ایمنی و امنیت عمومی | فیزیک | جغرافیا | مهندسی و فناوری | مدیریت و امور اداری | مخابرات | زبان انگلیسی | رایانه و الکترونیک | پرسنلی و منابع انسانی</t>
+          <t>ریاضیات | ایمنی و امنیت عمومی | فیزیک | جغرافیا | مهندسی و فناوری | مدیریت و اداره | مخابرات | زبان انگلیسی | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار | اشتراک زمانی | تجسم فضایی | استدلال ریاضی | کار با اعداد | جهت‌یابی فضایی | زمان واکنش</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | استدلال ریاضی | توانایی عددی | جهت‌گیری فضایی | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و کارشناسان بررسی صحنه جرم | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حراست | افسران و ماموران مراقبت در زندان‌ها | مدیران مدیریت بحران و شرایط اضطراری | بازرسان و ماموران حفاظت و بازرسی فرودگاهی | تکنسین‌های فوریت‌های پزشکی (اورژانس) | مدیران عمومی و مدیران عملیات | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با قوانین | تکنسین‌های نقشه‌برداری | کارشناسان و مجریان تخریب، انفجار و نگهداری مهمات | کارشناسان پاک‌سازی و امحای مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مخابرات | رایانه و الکترونیک | ایمنی و امنیت عمومی | مدیریت و امور اداری | جغرافیا | زبان انگلیسی | حمل‌ونقل | مهندسی و فناوری | ارتباطات و رسانه | پرسنلی و منابع انسانی</t>
+          <t>مخابرات | رایانه و الکترونیک | ایمنی و امنیت عمومی | مدیریت و اداره | جغرافیا | زبان انگلیسی | حمل و نقل | مهندسی و فناوری | ارتباطات و رسانه | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار | اشتراک زمانی | تجسم فضایی | توجه شنوایی | سرعت ادراک | انعطاف‌پذیری در جمع‌بندی | سرعت جمع‌بندی ذهنی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | توجه شنیداری | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری و هوانوردی عمومی | مراقبان پرواز (کنترلرهای ترافیک هوایی) | کارشناسان عملیات هوانوردی و فرودگاهی | مکانیک‌ها و تکنسین‌های تعمیر و نگهداری هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | مهندسان هوافضا | تکنسین‌ها و کارشناسان فناوری مهندسی هوافضا | مدیران مدیریت بحران و شرایط اضطراری | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و زنجیره تامین | مدیران عمومی و مدیران عملیات | مدیران عامل و ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و کارشناسان بررسی صحنه جرم | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | بازرسان و ماموران حفاظت و بازرسی فرودگاهی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
+          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری | کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مهندسان هوافضا | کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مدیران مدیریت بحران و پدافند غیرعامل | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران کل و مدیران عملیات | مدیران عامل و مدیران ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | مدیریت و امور اداری | مخابرات | زبان انگلیسی | پرسنلی و منابع انسانی | آموزش و تدریس | حمل‌ونقل | روان‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | مدیریت و اداره | مخابرات | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | حمل و نقل | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار | اشتراک زمانی | تجسم فضایی | جهت‌یابی فضایی | استقامت بدنی | قدرت ایستا | هماهنگی عمومی بدن | زمان واکنش</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و کارشناسان بررسی صحنه جرم | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حراست | افسران و ماموران مراقبت در زندان‌ها | مدیران مدیریت بحران و شرایط اضطراری | بازرسان و ماموران حفاظت و بازرسی فرودگاهی | تکنسین‌های فوریت‌های پزشکی (اورژانس) | مدیران عمومی و مدیران عملیات | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با قوانین | تکنسین‌های نقشه‌برداری | کارشناسان و مجریان تخریب، انفجار و نگهداری مهمات | کارشناسان پاک‌سازی و امحای مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | زبان‌های خارجی | مدیریت و امور اداری | مخابرات | جامعه‌شناسی و مردم‌شناسی | زبان انگلیسی | آموزش و تدریس | روان‌شناسی | حمل‌ونقل</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | زبان خارجی | مدیریت و اداره | مخابرات | جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار | اشتراک زمانی | تجسم فضایی | جهت‌یابی فضایی | استقامت بدنی | قدرت ایستا | هماهنگی عمومی بدن | زمان واکنش | توانایی حفظ و یادآوری</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | زمان عکس‌العمل | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و کارشناسان بررسی صحنه جرم | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حراست | افسران و ماموران مراقبت در زندان‌ها | مدیران مدیریت بحران و شرایط اضطراری | بازرسان و ماموران حفاظت و بازرسی فرودگاهی | تکنسین‌های فوریت‌های پزشکی (اورژانس) | مدیران عمومی و مدیران عملیات | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با قوانین | تکنسین‌های نقشه‌برداری | کارشناسان و مجریان تخریب، انفجار و نگهداری مهمات | کارشناسان پاک‌سازی و امحای مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | جغرافیا | مخابرات | زبان انگلیسی | پرسنلی و منابع انسانی | آموزش و تدریس | حمل‌ونقل</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | جغرافیا | مخابرات | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | حمل و نقل</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار | اشتراک زمانی | تجسم فضایی | جهت‌یابی فضایی | زمان واکنش | استقامت بدنی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | زمان عکس‌العمل | استقامت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و کارشناسان بررسی صحنه جرم | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حراست | افسران و ماموران مراقبت در زندان‌ها | مدیران مدیریت بحران و شرایط اضطراری | بازرسان و ماموران حفاظت و بازرسی فرودگاهی | تکنسین‌های فوریت‌های پزشکی (اورژانس) | مدیران عمومی و مدیران عملیات | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با قوانین | تکنسین‌های نقشه‌برداری | کارشناسان و مجریان تخریب، انفجار و نگهداری مهمات | کارشناسان پاک‌سازی و امحای مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | مکانیک | مخابرات | مدیریت و امور اداری | آموزش و تدریس | زبان انگلیسی | رایانه و الکترونیک | پرسنلی و منابع انسانی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | مخابرات | مدیریت و اداره | آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار | اشتراک زمانی | تجسم فضایی | توجه شنوایی | زمان واکنش | چابکی دستی | کنترل دقیق</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | توجه شنیداری | زمان عکس‌العمل | مهارت دستی | دقت کنترل</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری و هوانوردی عمومی | مراقبان پرواز (کنترلرهای ترافیک هوایی) | کارشناسان عملیات هوانوردی و فرودگاهی | مکانیک‌ها و تکنسین‌های تعمیر و نگهداری هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | مهندسان هوافضا | تکنسین‌ها و کارشناسان فناوری مهندسی هوافضا | مدیران مدیریت بحران و شرایط اضطراری | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و زنجیره تامین | مدیران عمومی و مدیران عملیات | مدیران عامل و ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و کارشناسان بررسی صحنه جرم | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | بازرسان و ماموران حفاظت و بازرسی فرودگاهی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
+          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری | کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مهندسان هوافضا | کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مدیران مدیریت بحران و پدافند غیرعامل | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران کل و مدیران عملیات | مدیران عامل و مدیران ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مکانیک | مهندسی و فناوری | مدیریت و امور اداری | آموزش و تدریس | فیزیک | زبان انگلیسی | رایانه و الکترونیک | پرسنلی و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | مهندسی و فناوری | مدیریت و اداره | آموزش و پرورش | فیزیک | زبان انگلیسی | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار | اشتراک زمانی | تجسم فضایی | چابکی دستی | تسلط و پایداری دست و بازو | کنترل دقیق | زمان واکنش | قدرت ایستا</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | مهارت دستی | ثبات دست و بازو | دقت کنترل | زمان عکس‌العمل | قدرت ایستا</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های تعمیر و نگهداری هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات سنگین متحرک (به‌جز موتور) | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی (به‌جز نصابان خطوط) | نصابان و تعمیرکاران رادیویی، بی‌سیم و دکل‌های مخابراتی | ریگرها و متخصصان اتصالات و مهار بار | اپراتورهای جرثقیل و دکل‌های بالابر | اپراتورهای ماشین‌آلات سنگین راه‌سازی و ساختمانی | مهندسان موتورخانه کشتی و شناور | ملوانان و نیروهای فنی موتورخانه شناور | کاپیتان‌ها، افسران و سکان‌داران شناورهای دریایی | کارشناسان عملیات هوانوردی و فرودگاهی | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عمومی و مدیران عملیات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان و مجریان تخریب، انفجار و نگهداری مهمات</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک‌های ماشین‌آلات صنعتی | مکانیک تجهیزات سنگین متحرک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | مهندسان فنی کشتی | ملوانان و روغن‌کاران شناورهای دریایی | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | کارشناسان عملیات فرودگاهی | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران کل و مدیران عملیات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان مواد منفجره و آتش‌باری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | آموزش و تدریس | جغرافیا | مخابرات | زبان انگلیسی | پرسنلی و منابع انسانی | حمل‌ونقل | روان‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | آموزش و پرورش | جغرافیا | مخابرات | زبان انگلیسی | پرسنل و منابع انسانی | حمل و نقل | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار | اشتراک زمانی | تجسم فضایی | جهت‌یابی فضایی | زمان واکنش | استقامت بدنی | قدرت ایستا</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | زمان عکس‌العمل | استقامت | قدرت ایستا</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و کارشناسان بررسی صحنه جرم | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حراست | افسران و ماموران مراقبت در زندان‌ها | مدیران مدیریت بحران و شرایط اضطراری | بازرسان و ماموران حفاظت و بازرسی فرودگاهی | تکنسین‌های فوریت‌های پزشکی (اورژانس) | مدیران عمومی و مدیران عملیات | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با قوانین | تکنسین‌های نقشه‌برداری | کارشناسان و مجریان تخریب، انفجار و نگهداری مهمات | کارشناسان پاک‌سازی و امحای مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مکانیک | مخابرات | ایمنی و امنیت عمومی | رایانه و الکترونیک | زبان انگلیسی | جغرافیا | مهندسی و فناوری</t>
+          <t>حمل و نقل | مکانیک | مخابرات | ایمنی و امنیت عمومی | رایانه و الکترونیک | زبان انگلیسی | جغرافیا | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید دور | دید نزدیک | توجه انتخابی | زمان واکنش | مرتب‌سازی اطلاعات | استدلال استقرایی | توجه شنوایی | هماهنگی چند عضو بدن | جهت‌یابی فضایی | استقامت بدنی | قدرت ایستا | هماهنگی عمومی بدن | ادراک عمق | اشتراک زمانی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری و هوانوردی عمومی | مراقبان پرواز (کنترلرهای ترافیک هوایی) | کارشناسان عملیات هوانوردی و فرودگاهی | مکانیک‌ها و تکنسین‌های تعمیر و نگهداری هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | مهندسان هوافضا | تکنسین‌ها و کارشناسان فناوری مهندسی هوافضا | مدیران مدیریت بحران و شرایط اضطراری | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و زنجیره تامین | مدیران عمومی و مدیران عملیات | مدیران عامل و ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و کارشناسان بررسی صحنه جرم | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | بازرسان و ماموران حفاظت و بازرسی فرودگاهی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
+          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری | کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مهندسان هوافضا | کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مدیران مدیریت بحران و پدافند غیرعامل | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران کل و مدیران عملیات | مدیران عامل و مدیران ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل‌ونقل | فیزیک | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل و نقل | فیزیک | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید دور | دید نزدیک | توجه انتخابی | زمان واکنش | مرتب‌سازی اطلاعات | استدلال استقرایی | توجه شنوایی | هماهنگی چند عضو بدن | جهت‌یابی فضایی | استقامت بدنی | قدرت ایستا | هماهنگی عمومی بدن | ادراک عمق | اشتراک زمانی | چابکی دستی | تسلط و پایداری دست و بازو | کنترل دقیق</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | مهارت دستی | ثبات دست و بازو | دقت کنترل</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های تعمیر و نگهداری هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات سنگین متحرک (به‌جز موتور) | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی (به‌جز نصابان خطوط) | نصابان و تعمیرکاران رادیویی، بی‌سیم و دکل‌های مخابراتی | ریگرها و متخصصان اتصالات و مهار بار | اپراتورهای جرثقیل و دکل‌های بالابر | اپراتورهای ماشین‌آلات سنگین راه‌سازی و ساختمانی | مهندسان موتورخانه کشتی و شناور | ملوانان و نیروهای فنی موتورخانه شناور | کاپیتان‌ها، افسران و سکان‌داران شناورهای دریایی | کارشناسان عملیات هوانوردی و فرودگاهی | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عمومی و مدیران عملیات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان و مجریان تخریب، انفجار و نگهداری مهمات</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک‌های ماشین‌آلات صنعتی | مکانیک تجهیزات سنگین متحرک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | مهندسان فنی کشتی | ملوانان و روغن‌کاران شناورهای دریایی | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | کارشناسان عملیات فرودگاهی | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران کل و مدیران عملیات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان مواد منفجره و آتش‌باری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
